--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="207">
   <si>
     <r>
       <rPr>
@@ -2761,30 +2761,58 @@
       <rPr>
         <sz val="8"/>
         <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円（税抜）は他社比</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.3</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で更新】基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/1</t>
     </r>
     <r>
       <rPr>
@@ -2803,73 +2831,168 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍。期間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月・ベンダー評価／非システム課題／効果試算までのスコープ拡張が要因だが、貴社が定義した「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月・成果物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点」に対応する金額が切り出されておらず、書面では妥当性を検証できない。基準スコープの切り出し見積りを質疑で要求。</t>
+      <t xml:space="preserve">12/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ベンダー評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非システム課題・効果試算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)2,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円に切り出され、検証可能になった点は評価。ただし基本スコープのみでも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍。品質点あたりコスト（後述）でも他社を上回り、価格妥当性の疑義は残る。</t>
     </r>
   </si>
   <si>
@@ -5777,7 +5900,37 @@
     <t xml:space="preserve">備考</t>
   </si>
   <si>
-    <t xml:space="preserve">提示金額（税抜）</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提示金額（税抜）｟</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">｠</t>
+    </r>
   </si>
   <si>
     <r>
@@ -5914,6 +6067,113 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本スコープ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円
+＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ベンダー評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) 300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円
+＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非システム課題等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) 2,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円
+（全部含むと合計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
@@ -5927,11 +6187,86 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万円</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">スコープが各社異なるため、この金額の直接比較は不可</t>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で基本／オプションに切り出し。基本スコープだけでも他社の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">支援期間</t>
@@ -6059,11 +6394,20 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/1</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 9/1</t>
     </r>
     <r>
       <rPr>
@@ -6082,36 +6426,66 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">12/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月）
+オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A: 27/1/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">1/31</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月）</t>
-    </r>
   </si>
   <si>
     <r>
@@ -6182,7 +6556,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">月額換算（概算）</t>
+    <t xml:space="preserve">月額換算（概算・基本スコープのみ）</t>
   </si>
   <si>
     <r>
@@ -6339,7 +6713,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1,560</t>
+      <t xml:space="preserve">1,360</t>
     </r>
     <r>
       <rPr>
@@ -6371,7 +6745,72 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">期間差を除いた粗い比較。体制規模の差を含む</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期間差を正規化しても</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は他社の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍。単純な期間長さでは説明できない</t>
+    </r>
   </si>
   <si>
     <r>
@@ -6379,6 +6818,431 @@
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">品質点あたりコスト（見積額</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷Q</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">得点）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷29.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">74.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)
+92.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">113.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷46.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">品質が最高の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は、品質差を勘案してもなお最も割高。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②の約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
@@ -6475,26 +7339,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">発行 年内（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月）</t>
+      <t xml:space="preserve">発行 「年内」＝基本スコープ期間の末（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -6534,7 +7398,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社のみ</t>
+      <t xml:space="preserve">社のみ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で期日を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と明確化したが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末には未達</t>
     </r>
   </si>
   <si>
@@ -6554,7 +7494,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">含む（</t>
+      <t xml:space="preserve">オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
     </r>
     <r>
       <rPr>
@@ -6592,7 +7551,418 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月末まで）</t>
+      <t xml:space="preserve">月末まで、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で価格分離。除いても基本スコープ単体でなお他社より高い</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">非システム課題の整理・ロードマップ（ガバナンス・組織体制／サステナマネジメント／ロードマップ／効果試算）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）。ただし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のうち証憑・承認の統制要件のシステム要件化に必要な事前協議は基本スコープに残置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で価格分離。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の評価根拠（証跡・統制の機能要件化）は基本スコープに残るため品質評価への影響は限定的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">効果試算・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・経営上申支援</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">含まない（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Appendix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に方法論提示のみ）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含む（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">As-Is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実測ベースの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">精緻化・上申資料）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">オプション化により基準スコープからは除外済み</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">展開計画・定着計画・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案①②は含む（案③は含まない）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一部含む（システム化方針書＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、基本スコープ内）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社の案①②③の価格差の主要因</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">アーキテクチャ検討</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非機能要件の一部として整理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">案①②は素案作成を含む</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">システム構成案策定（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）を基本スコープに含む</t>
     </r>
   </si>
   <si>
@@ -6613,240 +7983,46 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社の金額を押し上げる主要因①</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">非システム課題の整理・ロードマップ（ガバナンス・内部統制・サステナマネジメント）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">含む</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社の金額を押し上げる主要因②</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">効果試算・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROI</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・経営上申支援</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">含まない（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Appendix</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に方法論提示のみ）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">含む（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">As-Is</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実測ベースの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">精緻化・上申資料）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社の金額を押し上げる主要因③</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">展開計画・定着計画・</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PJ</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">計画書</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案①②は含む（案③は含まない）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部含む（システム化方針書）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社の案①②③の価格差の主要因</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">アーキテクチャ検討</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非機能要件の一部として整理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">案①②は素案作成を含む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">システム構成案策定を含む</t>
+      <t xml:space="preserve">社は基本スコープの中でも作り込みが深い（稼働直後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数年後の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階設計）</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">攻め（経営活用）の要件化</t>
@@ -6883,49 +8059,57 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ユースケース</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件の絞り込み・基盤要件化まで含む</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">スコープの深さの差</t>
+      <t xml:space="preserve">出口設計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）でユースケース優先度評価まで基本スコープに残置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">オプション化後も攻めの要件化は基本スコープ内＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価への影響なし</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">実働体制</t>
@@ -7248,7 +8432,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">級、公認会計士含む）</t>
+      <t xml:space="preserve">級、公認会計士含む）
+※基本・オプション共通の体制表で、業務配分の内訳は非開示</t>
     </r>
   </si>
   <si>
@@ -7269,7 +8454,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社は管理・専門層が厚い＝金額を押し上げる主要因④</t>
+      <t xml:space="preserve">社は管理・専門層が厚い＝金額を押し上げる主要因。基本スコープに絞ってもこの体制のまま＝単価水準の高さが基本スコープの価格に直接反映</t>
     </r>
   </si>
   <si>
@@ -7348,7 +8533,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">倍の開きが生じ得る</t>
+      <t xml:space="preserve">倍の開きが生じ得る。品質点あたりコストの差はこれが主因と推定</t>
     </r>
   </si>
   <si>
@@ -7416,468 +8601,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">社の安さの一部は戦略価格。次フェーズ単価の確認が必要</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【金額差の構造（要約）】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">金額差＝①期間の差（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月：最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.67</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×②</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">スコープの差（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社のみベンダー評価・非システム課題・効果試算を含む／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社は案により展開計画等が増減）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×③</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">体制の厚み（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社はシニア・専門家層が厚い、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社は実働がジュニア</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×④</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ファーム単価水準（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Big4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・大手総合＞中堅独立系）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×⑤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">値引き（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社▲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">粗い試算：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社から「ベンダー評価＋非システム課題＋効果試算＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月分」を除き</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月相当に換算すると概ね</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4,500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5,500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円規模と推定され、それでも残る対</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社との差は主に体制の厚みと単価水準の差。</t>
     </r>
   </si>
   <si>
@@ -7889,7 +8612,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">【</t>
+      <t xml:space="preserve">【金額差の構造（要約）｟</t>
     </r>
     <r>
       <rPr>
@@ -7900,7 +8623,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Apple to Apple</t>
+      <t xml:space="preserve">v1.1</t>
     </r>
     <r>
       <rPr>
@@ -7910,24 +8633,850 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">化のための</t>
-    </r>
+      <t xml:space="preserve">反映版｠】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【前提の更新】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で「基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ベンダー評価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非システム課題・効果試算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)2,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円」に価格分離。オプションを除いた基本スコープ単体でも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍であり、スコープ差（ベンダー評価・非システム課題）は主要因から後退し、残る差の主因は④体制の厚み（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/D/SM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">級アドバイザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名＋公認会計士を基本スコープにも配置）と⑤ファーム単価水準（大手総合＞中堅独立系・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Big4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）に集約される。①期間差（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月）は月額換算後も約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍の差が残り、単純な期間長さでは説明できない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【品質を勘案した検証】品質点あたりコスト（見積額</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">得点）で見ると、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rise 82.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案② </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">74.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) 113.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は品質が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最高（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">46.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点）だが、品質差を勘案してもなお最も割高（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②比約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍）。つまり「品質が高いから高い」という説明は方向としては正しいが、価格差の全てを説明するものではなく、品質を上回る超過コストが体制の厚み・単価水準に起因して残っている。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3/Q4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">への影響】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のうち証憑・承認等の統制要件のシステム要件化に必要な事前協議は基本スコープに残置され、出口設計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）のユースケース優先度評価も基本スコープ内。守り・攻めいずれの品質評価根拠も基本スコープに残るため、オプション化後も</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の素点は変更しない。</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apple to Apple</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">化のための</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -7935,7 +9484,37 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">① 基準スコープの固定</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">① 基準スコープの固定〔</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は一部対応済み〕</t>
+    </r>
   </si>
   <si>
     <r>
@@ -8116,7 +9695,121 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社にはベンダー評価等の切り出し、</t>
+      <t xml:space="preserve">社は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">とオプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を既に分離済み——ただし基本スコープ自体が他社の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍のままであり、①分離では解決せず、②の単価内訳開示が必須。</t>
     </r>
     <r>
       <rPr>
@@ -8196,7 +9889,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">② 工数・単価の統一フォーマット</t>
+    <t xml:space="preserve">② 工数・単価の統一フォーマット〔最優先〕</t>
   </si>
   <si>
     <r>
@@ -8321,6 +10014,44 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">の確定にも直結）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社は基本スコープに絞ってもなお割高であり、原因が「単価水準」か「投入人数・稼働率」かをこの内訳でしか切り分けられない。単価が同水準なら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">得点差（品質）で説明がつくが、単価そのものが高い場合は品質と無関係な割高要因として交渉対象にする。</t>
     </r>
   </si>
   <si>
@@ -9761,13 +11492,13 @@
         <v>55</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="14" t="n">
         <f aca="false">ROUND($D14*K14/5,1)</f>
-        <v>2.4</v>
-      </c>
-      <c r="M14" s="15" t="s">
+        <v>3.6</v>
+      </c>
+      <c r="M14" s="11" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9928,7 +11659,7 @@
       <c r="K18" s="19"/>
       <c r="L18" s="20" t="n">
         <f aca="false">ROUND(SUM(L14:L17),1)</f>
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
       <c r="M18" s="19"/>
     </row>
@@ -10180,7 +11911,7 @@
       <c r="K25" s="23"/>
       <c r="L25" s="24" t="n">
         <f aca="false">ROUND(L12+L18+L24,1)</f>
-        <v>75.4</v>
+        <v>76.6</v>
       </c>
       <c r="M25" s="23"/>
     </row>
@@ -10289,7 +12020,7 @@
       </c>
       <c r="E5" s="14" t="n">
         <f aca="false">'採点表（仮採点・理由）'!L18</f>
-        <v>12.6</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10329,7 +12060,7 @@
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">'採点表（仮採点・理由）'!L25</f>
-        <v>75.4</v>
+        <v>76.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10417,7 +12148,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -10460,10 +12191,10 @@
       <c r="C4" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="33" t="s">
         <v>131</v>
       </c>
     </row>
@@ -10477,7 +12208,7 @@
       <c r="C5" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="34" t="s">
@@ -10502,7 +12233,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="10" t="s">
         <v>142</v>
       </c>
       <c r="B7" s="33" t="s">
@@ -10514,21 +12245,21 @@
       <c r="D7" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="34" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="33" t="s">
         <v>150</v>
       </c>
       <c r="E8" s="33" t="s">
@@ -10540,58 +12271,58 @@
         <v>152</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="33" t="s">
         <v>162</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>165</v>
@@ -10599,179 +12330,208 @@
       <c r="D12" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="E12" s="33" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C13" s="33" t="s">
         <v>169</v>
       </c>
+      <c r="C13" s="34" t="s">
+        <v>170</v>
+      </c>
       <c r="D13" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="34" t="s">
         <v>171</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="D14" s="34" t="s">
         <v>176</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>179</v>
-      </c>
-      <c r="D15" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="E15" s="34" t="s">
+      <c r="D15" s="33" t="s">
         <v>181</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="B16" s="34" t="s">
         <v>184</v>
       </c>
+      <c r="C16" s="33" t="s">
+        <v>185</v>
+      </c>
       <c r="D16" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
+    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>191</v>
+      </c>
     </row>
-    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
     </row>
-    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
       <c r="E20" s="37"/>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+    <row r="21" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
     </row>
-    <row r="23" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
+    <row r="22" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
     </row>
-    <row r="24" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
+    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
+        <v>197</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
     </row>
     <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
+        <v>199</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
+        <v>201</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+    </row>
+    <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+    </row>
+    <row r="29" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="274">
   <si>
     <r>
       <rPr>
@@ -5894,10 +5894,1667 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※金額比較の前に、まず成果物レベルでスコープの広さ・深さを照合する（下表）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社の「基本スコープ」は同じ深さではなく、ズレは双方向（アビームが広い部分／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が広い部分の両方が存在）であり、金額差を単純にスコープだけで説明することはできない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">① 成果物カバレッジ比較（基本スコープ内で明示されているか）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成果物・タスク</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：ライズ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：アビーム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53M)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務要件定義書（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RACI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・承認プロセス・業務ルール）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○(1-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○(#5)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社共通</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">機能要件定義書（画面・帳票・データ連携・権限、独立文書）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含むか不明、独立文書として非明記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(#6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、独立文書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の案②価格表には独立タスクの明記なし</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">データ要件定義書（データ項目・粒度・マッピング・一次</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二次ソース区分）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">機能要件定義書の「情報・連携」に軽度含む</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(1-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">データ定義テンプレートは案①のみ、案②は対応なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(#7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、独立文書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アビームが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も深い</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">システム構成図・アーキテクチャ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">独立成果物なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(2-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、単一段階の素案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(#4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、稼働直後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数年後の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階設計</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ライズのみ欠落。アビームが最も深い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非機能要件定義書／システム要件定義書</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目体系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">独立文書として非明記</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○(#8)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ユースケース優先順位付け（攻めの絞り込み・効果</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実現性評価）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期仮説の提示のみ、優先度評価なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(Step2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降に後ろ倒し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">候補を事前評価済み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">アビームのみ実施済み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開示効率化検討（複数開示の共通化設計）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○(1-6)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本スコープに明記なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ含む</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">システム化方針（移行・テスト・教育・本番移行の方針）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非機能要件定義書に移行計画を記載</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">価格表に明記なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○(#9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アビームが最も深い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展開計画・定着計画（変更管理・トレーニング）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○(3-1,3-2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(Option B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に追い出し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は含むが、アビーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は含まない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書（体制・予算・全体スケジュール）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本紙内に含む</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○(4-1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本紙内に含むと推定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は独立成果物として明記</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">内部統制・保証人事前協議（証憑・統制要件の入口整理）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">△(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">証跡管理の言及のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">○(1-2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の一部を基本スコープに残置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ベンダー質疑応答・評価の実施</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">後続フェーズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">○(2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価方法検討まで。実施は案③以外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">✕(Option A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社とも実施そのものは価格表内で限定的</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【スコープ差の結論】アビームが広い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深い部分（データ要件定義書の独立化、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階アーキテクチャ、ユースケース優先順位付け、システム化方針の移行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テスト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育）は主にライズとの比較で価格差の一部を正当化する。一方、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が既に含み、アビーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には含まれない部分（開示効率化検討、展開計画・定着計画、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書の明示的な独立成果物化）もあり、この軸ではアビームの方が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">より狭いスコープでより高い価格になっている。スコープの広さ・深さは双方向にズレており、金額差（アビームが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.96</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍）をスコープだけで説明することはできない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">② 金額の直接比較</t>
+  </si>
+  <si>
     <t xml:space="preserve">比較項目</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考</t>
   </si>
   <si>
     <r>
@@ -6842,7 +8499,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">得点）</t>
+      <t xml:space="preserve">得点）※スコープ差を含む粗い指標</t>
     </r>
   </si>
   <si>
@@ -7177,7 +8834,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">品質が最高の</t>
+      <t xml:space="preserve">①成果物カバレッジ比較のとおりスコープは同一でないため、この数値はスコープ差込みの粗い指標。ただし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②は展開計画・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書等アビームの基本スコープにない成果物を含んだ上でなおこの単価であり、スコープ差を考慮しても</t>
     </r>
     <r>
       <rPr>
@@ -7196,45 +8891,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社は、品質差を勘案してもなお最も割高。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PwC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案②の約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍</t>
+      <t xml:space="preserve">社の割高感は残る</t>
     </r>
   </si>
   <si>
@@ -8644,6 +10301,226 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">【スコープ差の確認結果（①の表）】アビームの基本スコープは、ライズに対しては明確に広い・深い（独立したデータ要件定義書、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階アーキテクチャ、ユースケース優先順位付け、システム化方針の移行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">テスト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育）。一方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に対しては、開示効率化検討・展開計画・定着計画・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書という、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円には含まれる成果物が、アビームの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円の基本スコープには</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Option B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に追い出されており含まれない。つまりスコープ差は双方向にズレており、「アビームは範囲が広いから高い」という単純な説明は成立しない（対</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">では範囲が狭いのに高い）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">【前提の更新】</t>
     </r>
     <r>
@@ -8853,7 +10730,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">倍であり、スコープ差（ベンダー評価・非システム課題）は主要因から後退し、残る差の主因は④体制の厚み（</t>
+      <t xml:space="preserve">倍であり、残る差の主因は体制の厚み（</t>
     </r>
     <r>
       <rPr>
@@ -8891,7 +10768,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">名＋公認会計士を基本スコープにも配置）と⑤ファーム単価水準（大手総合＞中堅独立系・</t>
+      <t xml:space="preserve">名＋公認会計士を基本スコープにも配置）とファーム単価水準（大手総合＞中堅独立系・</t>
     </r>
     <r>
       <rPr>
@@ -8910,7 +10787,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）に集約される。①期間差（</t>
+      <t xml:space="preserve">）に集約される。期間差（</t>
     </r>
     <r>
       <rPr>
@@ -9035,7 +10912,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">得点）で見ると、</t>
+      <t xml:space="preserve">得点、スコープ差込みの粗い指標）で見ると、</t>
     </r>
     <r>
       <rPr>
@@ -9263,7 +11140,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点）だが、品質差を勘案してもなお最も割高（</t>
+      <t xml:space="preserve">点）だが、品質差・スコープ差の両方を勘案してもなお最も割高（</t>
     </r>
     <r>
       <rPr>
@@ -9301,7 +11178,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">倍）。つまり「品質が高いから高い」という説明は方向としては正しいが、価格差の全てを説明するものではなく、品質を上回る超過コストが体制の厚み・単価水準に起因して残っている。</t>
+      <t xml:space="preserve">倍）。つまり「品質が高いから高い」という説明は方向としては正しいが、価格差の全てを説明するものではなく、品質・スコープを上回る超過コストが体制の厚み・単価水準に起因して残っている。</t>
     </r>
   </si>
   <si>
@@ -10342,6 +12219,163 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">社の「変更の可能性」注記をすべて解消してから価格を比較する）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⑥ スコープ差の相殺確認〔新規〕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には含まれる「開示効率化検討・展開計画・定着計画・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書」が、アビームの基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(53M)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には含まれず</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Option B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に追い出されている。アビームには「なぜ自社の基本スコープは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">より狭いのに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">なのか」を工数内訳（②）とセットで説明させる。逆にライズには「独立したデータ要件定義書・アーキテクチャ図・ユースケース優先順位付けが成果物にない」ことを指摘し、不足時の追加費用を確認する。</t>
     </r>
   </si>
 </sst>
@@ -10354,7 +12388,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10521,6 +12555,29 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -10609,7 +12666,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10734,6 +12791,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10756,10 +12837,6 @@
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -12148,7 +14225,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -12164,374 +14241,653 @@
       <c r="D1" s="25"/>
       <c r="E1" s="25"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="31" t="s">
         <v>126</v>
       </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
     </row>
-    <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
         <v>127</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="32" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="D6" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="E6" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="34" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="s">
         <v>141</v>
       </c>
+      <c r="B7" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>145</v>
+      </c>
     </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="E7" s="34" t="s">
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="s">
         <v>146</v>
       </c>
+      <c r="B8" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="33" t="s">
+    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="s">
         <v>151</v>
       </c>
+      <c r="B9" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="11"/>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="34" t="s">
+    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="B10" s="15" t="s">
         <v>156</v>
       </c>
+      <c r="C10" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>159</v>
+    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>164</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="34" t="s">
+    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>163</v>
+      <c r="C13" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>173</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>167</v>
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>172</v>
-      </c>
+    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="E15" s="11"/>
     </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>177</v>
+    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>182</v>
-      </c>
+    <row r="17" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
     </row>
-    <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>187</v>
-      </c>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
     </row>
-    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="C17" s="34" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="E17" s="33" t="s">
+      <c r="B20" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
         <v>191</v>
       </c>
+      <c r="B21" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>195</v>
+      </c>
     </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>200</v>
+      </c>
     </row>
-    <row r="20" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>205</v>
+      </c>
     </row>
-    <row r="21" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
+    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>210</v>
+      </c>
     </row>
-    <row r="22" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>215</v>
+      </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+    <row r="26" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B26" s="40" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>220</v>
+      </c>
     </row>
-    <row r="25" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
+    <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>223</v>
+      </c>
     </row>
-    <row r="26" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+    <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>227</v>
+      </c>
     </row>
-    <row r="27" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
+    <row r="29" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>231</v>
+      </c>
     </row>
-    <row r="28" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
+    <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E30" s="39" t="s">
+        <v>236</v>
+      </c>
     </row>
-    <row r="29" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
+    <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="D33" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+    </row>
+    <row r="37" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+    </row>
+    <row r="38" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+    </row>
+    <row r="39" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+    </row>
+    <row r="40" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+    </row>
+    <row r="43" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+    </row>
+    <row r="44" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="40"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+    </row>
+    <row r="45" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+    </row>
+    <row r="46" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>269</v>
+      </c>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+    </row>
+    <row r="47" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+    </row>
+    <row r="48" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="17">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -11,6 +11,7 @@
     <sheet name="採点表（仮採点・理由）" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="サマリ" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="金額差分析" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="スコープ構造比較（難所別）" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="301">
   <si>
     <r>
       <rPr>
@@ -12376,6 +12377,2450 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">なのか」を工数内訳（②）とセットで説明させる。逆にライズには「独立したデータ要件定義書・アーキテクチャ図・ユースケース優先順位付けが成果物にない」ことを指摘し、不足時の追加費用を確認する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スコープ構造比較｜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの難所ベースの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">層フレームワーク</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【方法論】各社の提案書が使う成果物名・タスク名でベースラインを作ると、いずれか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社の粒度に比較が引き寄せられる（アンカリングバイアス）。これを避けるため、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社全員が自社の言葉に翻訳する前に必ず引用している貴社側の共通言語＝「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの難所」を層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の軸として採用する。層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">論点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成果物の独立性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深さ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">担当</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">層で見ることで、「含む</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">含まない」の○✕だけでは見えない深さの差（例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アーキテクチャ『素案』の中身が浅いか深いか）を捕捉する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【深さレベルの凡例】 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L0=</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前提として扱う</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検討しない</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1=</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">初期仮説の提示のみ／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2=</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検討方法論・設計手順の提示／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3=</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">具体的な設計・詳細ルールの確定／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L4=</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">詳細設計・物理設計まで</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">難所（層</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：貴社</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由来の共通言語）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：アビーム</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①ルールの策定
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">算定・開示要件の定義</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：初期仮説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの会計整理／前提パラメータ資産化／変更前提の柔軟設計）を提示し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に先行着手。担当＝中村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・アソシエイトパートナー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：「事前に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">様にて策定済みと想定」と前提化。本フェーズでの検討タスクなし。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（提案内に矛盾あり）：出口設計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Must/Should/Could×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">戦略依存の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">象限により線引き合意を最上流の意思決定点に設計＝方法論は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。一方、業務要件検討の前提としては「事前に策定済みと想定」＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の記述も併存。質疑で実際の検討範囲を確定要。担当＝山野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(M)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">②データ収集
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">データ所在の特定と入手</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：システム要件定義における基本方針に基づき整理（基本方針止まり、詳細化は次工程）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：収集項目特定→原始データ取得→提出データ変換→提出の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">フロー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの「よくある課題</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対応設計」まで具体化（拠点内排出源網羅・原始データフォーマット・期間不一致・単位変換・例外対応）。担当＝須貝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SM)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：拠点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設計（排出量・開示インパクト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">システム成熟度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">データ提出可否の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">軸）で収集方式（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API/CSV/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手入力）を振分け。入力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">簡素化・督促自動化。担当＝山野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平野。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ロジック実装
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">使える情報への変換</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：システム要件定義における基本方針に基づき整理（基本方針止まり）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：外部基準確認→未定義領域特定→統一ルール定義→妥当性確認の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ステップ＋移行条件確定（適用時期・遡及範囲・開示影響）まで具体化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：「事前に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">様にて策定済み想定」と前提化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ロジック資産の仕分け（残す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">移植</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">作り直す</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">捨てる、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）のみ基本スコープ内で対応。移行計画の要否検討に限定。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">④内部統制と承認フロー
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確からしさの担保</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：前提パラメータ台帳・変更管理方針書等を初期仮説として提示。版管理ルールの標準実装方針を明示。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：統制要素</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確認領域マトリクスで、責任所在・データ出所・完全性・妥当性の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">軸で「人の確認」と「システムの保持・追跡」の役割分担まで設計。担当＝須貝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アドバイザー陣。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（本体分離）：証憑統制要件の事前協議のみ基本スコープに残置（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の一部、担当＝張本・公認会計士）。キーコントロール定義・内部統制設計方針書の本格整理は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Option B(2,200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⑤データの可視化と活用
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">意思決定への昇華</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：初期仮説</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点（意思決定起点の設計／可変前提の設計／守攻一体化）を提示し、貴社と議論したい論点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つを列挙。担当＝中村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(SME)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。基本スコープ内。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降に後ろ倒し。本フェーズは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step1(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法定開示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を優先し明示的にスコープ外。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：攻めユースケース</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">候補を効果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実現性で事前評価し、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">件へ絞り込み・基盤要件化まで実施済み。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的。担当＝今野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・企業価値戦略</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。基本スコープ内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(#2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【難所別に見た各社の得意・不得意（層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の総合）】各社の「深さ」は難所ごとに大きく異なり、総花的に優れている会社はない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は②データ収集・③ロジック実装（業務プロセスの詳細設計）で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的だが、①ルール策定・⑤可視化活用（貴社の意思決定・戦略に関わる部分）は前提化・後ろ倒しにしており、「守りの実務設計は強いが、貴社の戦略判断そのものへの関与は薄い」という特徴を持つ。アビームは①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法論</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)⑤(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">攻め</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で最も具体的だが、④</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部統制の本格整理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">をオプションに切り出しており、「戦略判断への関与・攻めの設計は強いが、守りの実務を支える統制文書化は基本スコープから薄くなっている」という特徴を持つ。ライズは全難所で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（初期仮説・基本方針の提示）に留まり、詳細化は次工程（設計フェーズ）に委ねる設計——価格の安さと整合するが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末までにベンダーが精度良く見積れる詳細度に達しているかは、成果物ごとに質疑で確認が必要。</t>
     </r>
   </si>
 </sst>
@@ -12666,7 +15111,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -12836,6 +15281,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14897,4 +17346,155 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="38"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+    </row>
+    <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36" t="s">
+        <v>300</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A10:D10"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -12,6 +12,7 @@
     <sheet name="サマリ" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="金額差分析" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="スコープ構造比較（難所別）" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="価格ギャップと解消リクエスト" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="337">
   <si>
     <r>
       <rPr>
@@ -14821,6 +14822,1657 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">月末までにベンダーが精度良く見積れる詳細度に達しているかは、成果物ごとに質疑で確認が必要。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">価格ギャップの診断と解消リクエスト</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【方法】最も価格効率が良い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点・月）を基準レートとし、各社の品質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">得点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期間から「フェア価格」を逆算。実際の価格との差＝ギャップとし、ギャップの正体（①スコープ不足／②効率性の高さ＝むしろ深さを追加すべき／③単価・体制の超過）によって解消リクエストを変える。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：アビーム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">実際の価格／期間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実質月額レート（万円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点・月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27.40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（基準の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（基準）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29.04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（基準の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">品質・期間調整後フェア価格</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,805</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（基準そのもの）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,761</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ギャップ（実際−フェア）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">595</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,539</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+41%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ギャップの正体</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①スコープ不足の疑い（全難所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、独立アーキテクチャ図等が欠落）。安さの一部は幅の狭さで説明できるが、埋めると価格は上がる方向</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">②効率性が高い（このレートで①⑤の深さを追加すれば最良の選択肢になる）。ギャップは「価格を下げる」ではなく「深さを追加する」方向</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③単価・体制の超過（成果物カバレッジは他社と概ね相殺的＝スコープでは説明できない）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/D/SM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">級アドバイザーを基本スコープにも配置する体制構造が主因と推定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【会社別の解消リクエスト（具体的な依頼文）】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：ライズ
+スコープ完成のための増額見積りを要求する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①独立したシステム構成図・データ要件定義書・ユースケース優先順位付けを追加した場合の増額見積りを提出させる（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。完成後の想定価格は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,900</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円程度になると見込まれ、これでもなお最安値グループに残る可能性が高い。②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">値引きは戦略価格であり、次フェーズ（設計・開発</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PMO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）の単価をこの場でロックインさせる（値引きが「入口だけ」でないことの確認）。③このリクエストへの回答（増額の有無・金額）自体が、安さが「効率」か「スコープの手薄さ」かを判別する試験になる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深さ追加の増分見積りを要求する（最も低リスク・高</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">な一手）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①効率性が最も高いため、価格を下げるのではなく、弱点である難所①（能動的なルール策定支援）・難所⑤（可視化・活用の要件化）を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上まで追加した場合の増分見積りを要求する（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。このレートなら増分は数百万円〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円程度に収まる可能性が高く、その場合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円台前半で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も広く深いスコープを持つ提案に変わる。②案②の「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務要件定義書作成」に機能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">データ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">システム要件定義書相当が含まれるかを確定させ（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、含まれない場合は同時に見積りに追加させる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：アビーム
+単価是正または体制リバランスの二択を提示する</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①ランク別単価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稼働率の内訳開示（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">宿題）を前提に、ギャップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,539</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">41%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）の原因が単価そのものか、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/D/SM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">級の配置比率かを特定する。②単価是正案：フェア価格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,761</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円（≒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）を交渉のターゲットとして提示し、その価格でどのタスクを削らずに提供できるか回答させる。③体制リバランス案：単価を維持するなら、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Principal/Director</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">級の関与比率を下げ、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Manager/Senior Consultant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">級の実働比率を上げた体制表の再提出を求める（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と連動）。④いずれの案でも、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円に、アビームの独自</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階アーキテクチャ・独立データ要件定義書・ユースケース優先順位付け）の増分コストを加算した金額を「参照点」として提示し、それとの差額の説明を求める（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【推奨する交渉の順序】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（最優先・低リスク）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に①⑤深さ追加の増分見積りを依頼する。ダウンサイドがほぼなく、成功すれば最良の選択肢が生まれる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（並行）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アビームにランク別内訳の開示を依頼し、フェア価格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円を参照点として提示、単価是正か体制リバランスかの回答を求める。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（並行）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライズにスコープ完成の増額見積りを依頼し、次フェーズ単価のロックインを求める。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step4: 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社の再見積りが揃った時点で、成果物カバレッジ・難所別深さ・単価内訳のすべてが同じ基準スコープで比較できる状態になり、最終選定に進む。</t>
     </r>
   </si>
 </sst>
@@ -15111,7 +16763,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -15286,6 +16938,10 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -17497,4 +19153,218 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+    </row>
+    <row r="11" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="41" t="s">
+        <v>326</v>
+      </c>
+      <c r="B11" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+    </row>
+    <row r="12" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="41" t="s">
+        <v>328</v>
+      </c>
+      <c r="B12" s="40" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+    </row>
+    <row r="13" customFormat="false" ht="129.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="41" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="44" t="s">
+        <v>335</v>
+      </c>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -400,6 +400,34 @@
       <rPr>
         <sz val="8"/>
         <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4→3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に補正】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
@@ -527,7 +555,235 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">完了という貴社の時間軸理解にズレ。</t>
+      <t xml:space="preserve">完了という貴社の時間軸理解にズレ。さらに「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ご依頼事項（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理解）」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）では攻め（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Scope3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次データ改革・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開示スキーム）を正確に理解していると明記しながら、提案全体のアプローチ図「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アプローチ想定作成物」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）には攻め系の成果物ボックスが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つも存在しない。採点基準「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの難所を提案全体に反映しているか」に照らすと、理解の言明と提案全体の構造が一致していない裏付けなき主張（素点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上限）に該当するため補正。★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で解消要。</t>
     </r>
   </si>
   <si>
@@ -740,7 +996,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「戦略依存</t>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5→4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に補正】「戦略依存</t>
     </r>
     <r>
       <rPr>
@@ -854,7 +1129,140 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">兆円企業で開示・保証要件未確定下の適用実績を裏付けとして提示。</t>
+      <t xml:space="preserve">兆円企業で開示・保証要件未確定下の適用実績を裏付けとして提示。一方、難所①（ルール策定）について、業務要件検討の前提としては「事前に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">様にて策定済みと想定」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）とする記述と、出口設計（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">象限方法論により線引き合意を最上流に設計する（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）という記述が併存し、方法論を能動的に適用する範囲が確定していない。素点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の要件「裏付けが完全」に届かないため、採点ルール「素点に迷ったら低い方を付け」に従い補正。★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で解消要。</t>
     </r>
   </si>
   <si>
@@ -867,7 +1275,7 @@
     <t xml:space="preserve">証憑紐付け・多段階承認・変更履歴保全を機能要件へ落とす道筋と、手作業根絶のプロセス設計が具体的か</t>
   </si>
   <si>
-    <t xml:space="preserve">証憑紐付け要件定義・版管理・変更管理方針書等、成果物への道筋は示されるが記載は一般論の域。手作業根絶のプロセス設計の具体度と実績の裏付けが薄い。</t>
+    <t xml:space="preserve">証憑紐付け要件定義・版管理・変更管理方針書等、成果物への道筋は示されるが記載は一般論の域。手作業根絶のプロセス設計の具体度と実績の裏付けが薄い。加えて、独立したシステム構成図・アーキテクチャの成果物が成果物一覧に存在せず（成果物カバレッジ比較で確認）、統制のシステム実装面の検証手段も薄い。</t>
   </si>
   <si>
     <r>
@@ -953,7 +1361,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">拠点の統制構築実績が裏付け。</t>
+      <t xml:space="preserve">拠点の統制構築実績が裏付け。ただし「アプローチ想定作成物」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は攻めに全く触れず守り一色であり、守りの深さが提案全体の構造的な偏りの上に立っていることは留意（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参照）。</t>
     </r>
   </si>
   <si>
@@ -1002,7 +1448,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">」予防まで具体的。</t>
+      <t xml:space="preserve">」予防まで具体的。方法論の具体性自体は高いが、その成果物（内部統制設計方針書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は基本スコープでなくオプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に切り出されている点は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C1/D2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">側で評価（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で解消要）。</t>
     </r>
   </si>
   <si>
@@ -2066,7 +2588,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中村氏の専門性は高い。本人のコンペ出席と確定を質疑で要確認。</t>
+      <t xml:space="preserve">中村氏の専門性は高い。参画予定メンバー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名（田村・豊田・中村・渡辺）にシステム連携を主導した実務経験の明記がなく、技術検証の担い手が体制表上で特定できない（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。本人のコンペ出席と確定を質疑で要確認。</t>
     </r>
   </si>
   <si>
@@ -2248,7 +2808,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">で実名・経歴なし。成果物品質の大半を担う層が匿名であり、書面では実現性を判断できない。</t>
+      <t xml:space="preserve">で実名・経歴なし。成果物品質の大半を担う層が匿名であり、書面では実現性を判断できない。加えて、体制で最もシステム連携・アーキテクチャの実務経験が濃い小泉氏（要件定義〜設計〜開発〜展開に精通）が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">関与のアドバイザー層であり、技術的に最適な人材が実働に入らない可能性（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。</t>
     </r>
   </si>
   <si>
@@ -2373,7 +2971,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">、「参画メンバーは変更になる可能性」の注記あり。本人出席と交代条件を質疑で要確認。</t>
+      <t xml:space="preserve">、「参画メンバーは変更になる可能性」の注記あり。加えて、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SSBJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">向けシステム要件定義・導入実績を複数持つ森銅氏の稼働が体制表で「適宜」であり、最も技術経験が濃い人物の稼働率が最も低い可能性（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。本人出席と交代条件を質疑で要確認。</t>
     </r>
   </si>
   <si>
@@ -3862,7 +4498,140 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ヶ月完遂計画として成立していない。</t>
+      <t xml:space="preserve">ヶ月完遂計画として成立していない。加えて「アプローチ想定作成物」（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）では</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">作成が業務要件定義書・機能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非機能要求一覧・移行運用要求一覧・開示レポート一覧・アーキテクチャ素案・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書・展開方針という、ほぼ全ワークストリームの出力を統合する単一の終着点として設計されており、いずれか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つが遅延すれば</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発行全体が遅延するクリティカルパス集中構造（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で緩和策要確認）。</t>
     </r>
   </si>
   <si>
@@ -4900,7 +5669,37 @@
     <t xml:space="preserve">合計</t>
   </si>
   <si>
-    <t xml:space="preserve">【総評（書面ベース）】</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【総評（書面ベース・第</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">版）】</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4939,94 +5738,438 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）が突出。貴社固有の前提（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Cat11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・戦略並行・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逆算）の理解、アジャイル方法論、実名実績（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ホールディングス等）、公認会計士配置が強み。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　一方、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円は「</t>
+      <t xml:space="preserve">）が依然トップだが、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5→4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に補正（難所①の対応方針に提案書内の記述矛盾）。貴社固有の前提理解・アジャイル方法論・実名実績・公認会計士配置は強み。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">v1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で基本スコープ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＋オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に価格分離したが、基本スコープのみでも他社の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍。品質・期間調整後のフェア価格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(3,761</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">とのギャップは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+41%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。さらに提案コンセプト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P.2-3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が掲げる「守り＝証明できる体制」「攻め＝企業価値向上の実現」の証明工程（内部統制設計方針書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・効果試算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）自体がオプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に切り出されており、基本スコープでは自社の提案コンセプトを完遂できない可能性（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で解消要）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4→3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に補正（依頼理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と提案全体のアプローチ図</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.39</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の間で、攻めの反映有無に矛盾）。守りの設計力（統制・証跡）と導入実績の定量規模はトップ級。</t>
     </r>
     <r>
       <rPr>
@@ -5045,7 +6188,569 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ヶ月・成果物</t>
+      <t xml:space="preserve">案提示・稼働率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">開示など透明性は最良で、品質・期間調整後のフェア価格は基準そのもの（ギャップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も価格効率が良い。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　致命的な懸念は①実働</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稼働）が全員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TBD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝品質の担い手が不明（体制で最も経験豊富な小泉氏はアドバイザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">関与）、②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末（仮）＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末要求と不整合、③</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">作成への全ワークストリーム統合＝クリティカルパス集中構造、の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点。質疑での解消が採用の前提条件。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">■ A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社ライズ：唯一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">完成にコミットし絶対額も最安（値引後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）。ただし期間正規化した品質調整後フェア価格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1,805</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">との比較では実質</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のギャップがあり、「最安値」は必ずしも「最良の価格効率」を意味しない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">　全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">難所で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（初期仮説・基本方針）に留まり、独立したアーキテクチャ図・データ要件定義書・ユースケース優先順位付けが成果物一覧にない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SSBJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固有の会社実績が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点セットで示されず、主要メンバーが「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」表記で未確定、システム連携の実務経験を持つメンバーも見当たらない。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">値引きの実態確認が必要。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【コンペ質疑での必須確認事項（詳細は質問票 全</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">42</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">問を参照）】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・全社共通：貴社想定成果物</t>
     </r>
     <r>
       <rPr>
@@ -5064,7 +6769,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">点」の基準スコープ外（ベンダー評価・非システム課題・効果試算・</t>
+      <t xml:space="preserve">点との対応表／「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月末</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">発行完了」の達成可否と前提／ランク別単価</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">稼働率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">期間の内訳（統一フォーマット）／</t>
     </r>
     <r>
       <rPr>
@@ -5083,26 +6864,124 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ヶ月）を含み、切り出し見積りなしでは価格妥当性を検証できない。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発行も「年内」で</t>
+      <t xml:space="preserve">つの難所の自己採点（当社照合結果との差異）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：値引きの持続性（次フェーズ単価）／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・リードの確定と本人出席／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SSBJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">類似案件の会社実績／不足成果物（アーキテクチャ図等）の追加見積り</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：実働</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名の実名・経歴の提示／</t>
     </r>
     <r>
       <rPr>
@@ -5121,191 +7000,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月末未達。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">■ B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PwC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：守りの設計力（統制・証跡）と導入実績の定量規模はトップ級。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案提示・稼働率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">開示など透明性は最良。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　致命的な懸念は①実働</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稼働）が全員</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">TBD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝品質の担い手が不明、②</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末（仮）＝</t>
+      <t xml:space="preserve">月末完了へ前倒しした場合の体制・金額／依頼理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P.10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と実行計画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(P.28/P.39)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の攻め反映有無の矛盾解消／「提案スコープ」点線の境界明確化</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：基本スコープの単価内訳（ランク別）／</t>
     </r>
     <r>
       <rPr>
@@ -5324,379 +7087,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月末要求と不整合、の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点。質疑での解消が採用の前提条件。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">■ A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社ライズ：唯一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">完成にコミットし価格も最安（値引後</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2,400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万円）。「条件付き要件」の方法論は本件の特殊前提に整合。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">　ただし</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SSBJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">固有の会社実績が</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点セットで示されず、主要メンバーが「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">or</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」表記で未確定、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">値引きは安値の実態確認（体制・品質の維持可否）が必要。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【コンペ質疑での必須確認事項】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・全社共通：貴社想定成果物</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点との対応表／「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">発行完了」の達成可否と前提／ランク別単価</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">稼働率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">期間の内訳（統一フォーマット）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社：値引きの持続性（次フェーズ単価）／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・リードの確定と本人出席／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SSBJ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">類似案件の会社実績</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
+      <t xml:space="preserve">月末前倒しの可否／提案コンセプト</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">守り・攻め</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の証明工程がオプション</t>
     </r>
     <r>
       <rPr>
@@ -5715,151 +7144,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">社：実働</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">名の実名・経歴の提示／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末完了へ前倒しした場合の体制・金額／交代時の品質担保条件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社：基準スコープ（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RFP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">作成まで）の切り出し金額／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月末前倒しの可否／稼働率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と交代条件の明示</t>
+      <t xml:space="preserve">である理由／難所①の対応方針の記述矛盾解消</t>
     </r>
   </si>
   <si>
@@ -17352,13 +18637,13 @@
         <v>16</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I6" s="14" t="n">
         <f aca="false">ROUND($D6*H6/5,1)</f>
-        <v>4.8</v>
-      </c>
-      <c r="J6" s="15" t="s">
+        <v>3.6</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>17</v>
       </c>
       <c r="K6" s="13" t="n">
@@ -17406,11 +18691,11 @@
         <v>23</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="14" t="n">
         <f aca="false">ROUND($D7*K7/5,1)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>24</v>
@@ -17611,13 +18896,13 @@
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="n">
         <f aca="false">ROUND(SUM(I6:I11),1)</f>
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
       <c r="L12" s="20" t="n">
         <f aca="false">ROUND(SUM(L6:L11),1)</f>
-        <v>46.8</v>
+        <v>44.8</v>
       </c>
       <c r="M12" s="19"/>
     </row>
@@ -18087,13 +19372,13 @@
       <c r="H25" s="23"/>
       <c r="I25" s="24" t="n">
         <f aca="false">ROUND(I12+I18+I24,1)</f>
-        <v>64.4</v>
+        <v>63.2</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="24" t="n">
         <f aca="false">ROUND(L12+L18+L24,1)</f>
-        <v>76.6</v>
+        <v>74.6</v>
       </c>
       <c r="M25" s="23"/>
     </row>
@@ -18178,11 +19463,11 @@
       </c>
       <c r="D4" s="14" t="n">
         <f aca="false">'採点表（仮採点・理由）'!I12</f>
-        <v>36.4</v>
+        <v>35.2</v>
       </c>
       <c r="E4" s="14" t="n">
         <f aca="false">'採点表（仮採点・理由）'!L12</f>
-        <v>46.8</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18238,11 +19523,11 @@
       </c>
       <c r="D7" s="24" t="n">
         <f aca="false">'採点表（仮採点・理由）'!I25</f>
-        <v>64.4</v>
+        <v>63.2</v>
       </c>
       <c r="E7" s="24" t="n">
         <f aca="false">'採点表（仮採点・理由）'!L25</f>
-        <v>76.6</v>
+        <v>74.6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/SSBJ提案評価_採点・金額差分析.xlsx
+++ b/docs/SSBJ提案評価_採点・金額差分析.xlsx
@@ -13,6 +13,7 @@
     <sheet name="金額差分析" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="スコープ構造比較（難所別）" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="価格ギャップと解消リクエスト" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="総合対応表（全社）" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="441">
   <si>
     <r>
       <rPr>
@@ -17758,6 +17759,2649 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">社の再見積りが揃った時点で、成果物カバレッジ・難所別深さ・単価内訳のすべてが同じ基準スコープで比較できる状態になり、最終選定に進む。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総合対応表｜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社の基本・オプション区分（金額交渉用）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">凡例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: ●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝基本価格に含む／○</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">名称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝オプション扱い（該当する案・オプション名を付記）／△＝含まれるか提案書上で判断できない（要確認）／✕＝対応なし（スコープ外）。金額交渉では、✕・△・オプションの行を中心に「基準スコープに含めた場合の追加金額」を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社に確認する。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">分類</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：ライズ
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2,400</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC
+(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社：アビーム
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">53,000,000</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">交渉ポイント</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現状調査</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">As-Is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整理・不足補完</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">●</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、全案）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方針策定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">開示項目・収集データの絞り込み</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">系）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">算定ガイドライン・ロジックの見直し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●（基本方針止まり、浅い）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-2/1-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含む、詳細検討あり）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">△（前提化。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資産の仕分けのみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で対応）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アビームに難所①③の対応方針の矛盾を確認（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。深さは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が最も具体的</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">攻めユースケースの評価・絞り込み</t>
+  </si>
+  <si>
+    <t xml:space="preserve">●（初期仮説のみ、浅い）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">✕（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Step2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以降）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">候補を効果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実現性で評価済み・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に①⑤深さ追加の増分見積りを要求（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B8/B9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務・システム設計</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">To-Be</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業務フロー設計（承認・証跡）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、全案）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">海外拠点ヒアリング結果の統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">△（依存関係の言及のみ）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含むと推定）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ライズに統合の深さを確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">システム構成案・アーキテクチャ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（独立成果物なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○案①②のみ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、単一段階）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、稼働直後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数年後の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">段階設計）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライズに追加時の金額を確認（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A7/A9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">機能要件定義書（独立文書）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">△（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含むか不明）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の範囲を確認（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">データ要件定義書（独立文書）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（機能要件定義書に軽度含む）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○案①のみ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ライズ・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案②双方に不足。追加金額を確認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">非機能・システム要件定義書</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">項目体系）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">△（独立文書か不明）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">システム化方針（移行・テスト・教育）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">△（非機能要件定義書内に一部記載）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（価格表に明記なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・ライズに追加時の金額を確認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">開示効率化検討（複数開示の共通化）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○案①②のみ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（基本スコープに明記なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ対応。他社に必要性の有無を確認</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部統制・保証対応</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保証人との事前協議</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（明記なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含む）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の一部のみ）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ライズの対応状況を確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内部統制設計方針書・キーコントロール定義（正式文書）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（独立文書なし）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に含む、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社中最も具体的）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本体）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">アビームに提案コンセプト（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P.2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）との矛盾を確認（★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">効果・投資対効果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">効果試算・経営報告資料（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ROI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">✕（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Appendix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方法論の提示のみ）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社とも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（費用対効果）の定量化余地あり</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">F. </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">展開・定着・</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">管理</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">展開計画・定着計画</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○案①②のみ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3-1,3-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">✕（非システム論点整理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">はオプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">だが業務展開計画としては明記なし）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のみ対応。金額差の一因（案①②③の差）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PJ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計画書（体制・予算・スケジュール）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">△（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本紙内に含む）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○案①②のみ（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">△（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本紙内に含むと推定、独立文書なし）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G. RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・ベンダー選定</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RFP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本紙作成・提示</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、全案）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">#10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、提示のみ）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社共通で「提示」までが基本。実施・評価は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">G2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参照</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ベンダー質疑対応・評価・選定支援</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✕（後続フェーズと明記）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">△（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">評価方法検討はあるが実施は不明）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">○オプション</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">全社に評価実施の有無・金額を統一様式で確認</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【集計】○△✕の行数（多いほど基準スコープからの抜け漏れ・要確認事項が多い）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">●で完全に基本価格に含まれない行数（○</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/△/✕</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の合計）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">11/19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7/19</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">【金額交渉での使い方（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ステップ）】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">①この表の✕・△・オプション行を、各社への「基準スコープに含めた場合の追加金額」の見積り依頼リストとして使う（質問票★</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A7/★A9/★B6/★B8/★B9/★C10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と対応）。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">②3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社から回答が揃った時点で、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行すべてが●（基本に含む）になった状態の「完全版基準スコープ」の金額を再構成する。これが本当の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Apple to Apple</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比較値になる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③完全版の金額と、価格ギャップ分析（品質・期間調整後フェア価格：ライズ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,805</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PwC2,700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円／アビーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,761</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万円）を突き合わせ、なお残る差額を単価・体制の交渉材料にする。</t>
     </r>
   </si>
 </sst>
@@ -18048,7 +20692,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -18227,6 +20871,22 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -20652,4 +23312,555 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+    </row>
+    <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="45" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11"/>
+      <c r="B5" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+    </row>
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11"/>
+      <c r="B11" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="45" t="s">
+        <v>398</v>
+      </c>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+    </row>
+    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="45" t="s">
+        <v>414</v>
+      </c>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+    </row>
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11"/>
+      <c r="B26" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="45" t="s">
+        <v>423</v>
+      </c>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11"/>
+      <c r="B28" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="46" t="s">
+        <v>433</v>
+      </c>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="47"/>
+      <c r="B32" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="F32" s="47"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+    </row>
+    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="36" t="s">
+        <v>438</v>
+      </c>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+    </row>
+    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="44" t="s">
+        <v>439</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="36" t="s">
+        <v>440</v>
+      </c>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A37:F37"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>